--- a/bin/retainer.xlsx
+++ b/bin/retainer.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="retainer" sheetId="1" r:id="rId1"/>
@@ -629,22 +629,22 @@
       </c>
       <c r="C2">
         <f ca="1">VLOOKUP(F2,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>638</v>
+        <v>1884</v>
       </c>
       <c r="D2">
-        <f ca="1">ROUNDUP(RAND() * 100, 0)/100</f>
-        <v>0.6</v>
+        <f ca="1">ROUNDUP(RAND()*100, 2)</f>
+        <v>64.12</v>
       </c>
       <c r="E2" s="2">
         <v>45590</v>
       </c>
       <c r="F2">
         <f ca="1">ROUNDUP(RAND()*25, 0)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G2" t="str">
         <f ca="1">CONCATENATE("(",B2,", ", C2, ", ", D2, ", ", CHAR(39),  TEXT(E2, "yyyy-mm-dd"), "'),")</f>
-        <v>(78, 638, 0.6, '2024-10-25'),</v>
+        <v>(78, 1884, 64.12, '2024-10-25'),</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -656,22 +656,22 @@
       </c>
       <c r="C3">
         <f ca="1">VLOOKUP(F3,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1896</v>
+        <v>1884</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D26" ca="1" si="0">ROUNDUP(RAND() * 100, 0)/100</f>
-        <v>0.64</v>
+        <f t="shared" ref="D3:D26" ca="1" si="0">ROUNDUP(RAND()*100, 2)</f>
+        <v>2.2699999999999996</v>
       </c>
       <c r="E3" s="2">
         <v>45602</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F26" ca="1" si="1">ROUNDUP(RAND()*25, 0)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" ref="G3:G26" ca="1" si="2">CONCATENATE("(",B3,", ", C3, ", ", D3, ", ", CHAR(39),  TEXT(E3, "yyyy-mm-dd"), "'),")</f>
-        <v>(17, 1896, 0.64, '2024-11-06'),</v>
+        <v>(17, 1884, 2.27, '2024-11-06'),</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -683,22 +683,22 @@
       </c>
       <c r="C4">
         <f ca="1">VLOOKUP(F4,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>638</v>
+        <v>92</v>
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>0.09</v>
+        <v>96.77000000000001</v>
       </c>
       <c r="E4" s="2">
         <v>45628</v>
       </c>
       <c r="F4">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(76, 638, 0.09, '2024-12-02'),</v>
+        <v>(76, 92, 96.77, '2024-12-02'),</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -710,22 +710,22 @@
       </c>
       <c r="C5">
         <f ca="1">VLOOKUP(F5,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>548</v>
+        <v>346</v>
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>0.25</v>
+        <v>91.59</v>
       </c>
       <c r="E5" s="2">
         <v>45684</v>
       </c>
       <c r="F5">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(74, 548, 0.25, '2025-01-27'),</v>
+        <v>(74, 346, 91.59, '2025-01-27'),</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -737,22 +737,22 @@
       </c>
       <c r="C6">
         <f ca="1">VLOOKUP(F6,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>92</v>
+        <v>723</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>0.74</v>
+        <v>5.7799999999999994</v>
       </c>
       <c r="E6" s="2">
         <v>45693</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(9, 92, 0.74, '2025-02-05'),</v>
+        <v>(9, 723, 5.78, '2025-02-05'),</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -764,22 +764,22 @@
       </c>
       <c r="C7">
         <f ca="1">VLOOKUP(F7,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>222</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>0.33</v>
+        <v>38.86</v>
       </c>
       <c r="E7" s="2">
         <v>45749</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(79, 222, 0.33, '2025-04-02'),</v>
+        <v>(79, 50, 38.86, '2025-04-02'),</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -791,22 +791,22 @@
       </c>
       <c r="C8">
         <f ca="1">VLOOKUP(F8,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1674</v>
+        <v>123</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>0.92</v>
+        <v>83.61</v>
       </c>
       <c r="E8" s="2">
         <v>45750</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(4, 1674, 0.92, '2025-04-03'),</v>
+        <v>(4, 123, 83.61, '2025-04-03'),</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -818,22 +818,22 @@
       </c>
       <c r="C9">
         <f ca="1">VLOOKUP(F9,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>222</v>
+        <v>1341</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>2.48</v>
       </c>
       <c r="E9" s="2">
         <v>45757</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(62, 222, 0.14, '2025-04-10'),</v>
+        <v>(62, 1341, 2.48, '2025-04-10'),</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -845,22 +845,22 @@
       </c>
       <c r="C10">
         <f ca="1">VLOOKUP(F10,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>346</v>
+        <v>1091</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>0.21</v>
+        <v>22.76</v>
       </c>
       <c r="E10" s="2">
         <v>45763</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(63, 346, 0.21, '2025-04-16'),</v>
+        <v>(63, 1091, 22.76, '2025-04-16'),</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -872,22 +872,22 @@
       </c>
       <c r="C11">
         <f ca="1">VLOOKUP(F11,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1992</v>
+        <v>804</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.31</v>
+        <v>84.240000000000009</v>
       </c>
       <c r="E11" s="2">
         <v>45778</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(24, 1992, 0.31, '2025-05-01'),</v>
+        <v>(24, 804, 84.24, '2025-05-01'),</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
       </c>
       <c r="C12">
         <f ca="1">VLOOKUP(F12,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1520</v>
+        <v>1884</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>0.42</v>
+        <v>69.540000000000006</v>
       </c>
       <c r="E12" s="2">
         <v>45783</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1, 1520, 0.42, '2025-05-06'),</v>
+        <v>(1, 1884, 69.54, '2025-05-06'),</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -926,22 +926,22 @@
       </c>
       <c r="C13">
         <f ca="1">VLOOKUP(F13,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>92</v>
+        <v>346</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>0.77</v>
+        <v>55.809999999999995</v>
       </c>
       <c r="E13" s="2">
         <v>45784</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(26, 92, 0.77, '2025-05-07'),</v>
+        <v>(26, 346, 55.81, '2025-05-07'),</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -953,22 +953,22 @@
       </c>
       <c r="C14">
         <f ca="1">VLOOKUP(F14,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1674</v>
+        <v>638</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>0.02</v>
+        <v>14.379999999999999</v>
       </c>
       <c r="E14" s="2">
         <v>45785</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(71, 1674, 0.02, '2025-05-08'),</v>
+        <v>(71, 638, 14.38, '2025-05-08'),</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -980,22 +980,22 @@
       </c>
       <c r="C15">
         <f ca="1">VLOOKUP(F15,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1091</v>
+        <v>1362</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="E15" s="2">
         <v>45824</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(14, 1091, 0.14, '2025-06-16'),</v>
+        <v>(14, 1362, 3.8, '2025-06-16'),</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="C16">
         <f ca="1">VLOOKUP(F16,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1362</v>
+        <v>1773</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.96</v>
+        <v>39.809999999999995</v>
       </c>
       <c r="E16" s="2">
         <v>45828</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(2, 1362, 0.96, '2025-06-20'),</v>
+        <v>(2, 1773, 39.81, '2025-06-20'),</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C17">
         <f ca="1">VLOOKUP(F17,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>717</v>
+        <v>1992</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>0.11</v>
+        <v>83.9</v>
       </c>
       <c r="E17" s="2">
         <v>45834</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(60, 717, 0.11, '2025-06-26'),</v>
+        <v>(60, 1992, 83.9, '2025-06-26'),</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C18">
         <f ca="1">VLOOKUP(F18,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>346</v>
+        <v>222</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.96</v>
+        <v>65.88000000000001</v>
       </c>
       <c r="E18" s="2">
         <v>45867</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(99, 346, 0.96, '2025-07-29'),</v>
+        <v>(99, 222, 65.88, '2025-07-29'),</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1088,22 +1088,22 @@
       </c>
       <c r="C19">
         <f ca="1">VLOOKUP(F19,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>222</v>
+        <v>123</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>0.56999999999999995</v>
+        <v>41.739999999999995</v>
       </c>
       <c r="E19" s="2">
         <v>45905</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(40, 222, 0.57, '2025-09-05'),</v>
+        <v>(40, 123, 41.74, '2025-09-05'),</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1115,22 +1115,22 @@
       </c>
       <c r="C20">
         <f ca="1">VLOOKUP(F20,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1538</v>
+        <v>723</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>0.35</v>
+        <v>22.860000000000003</v>
       </c>
       <c r="E20" s="2">
         <v>45911</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(80, 1538, 0.35, '2025-09-11'),</v>
+        <v>(80, 723, 22.86, '2025-09-11'),</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1142,22 +1142,22 @@
       </c>
       <c r="C21">
         <f ca="1">VLOOKUP(F21,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1341</v>
+        <v>50</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>0.06</v>
+        <v>49.29</v>
       </c>
       <c r="E21" s="2">
         <v>45916</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(82, 1341, 0.06, '2025-09-16'),</v>
+        <v>(82, 50, 49.29, '2025-09-16'),</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1169,22 +1169,22 @@
       </c>
       <c r="C22">
         <f ca="1">VLOOKUP(F22,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>123</v>
+        <v>1341</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="0"/>
-        <v>0.63</v>
+        <v>49.85</v>
       </c>
       <c r="E22" s="2">
         <v>45930</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(41, 123, 0.63, '2025-09-30'),</v>
+        <v>(41, 1341, 49.85, '2025-09-30'),</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1196,22 +1196,22 @@
       </c>
       <c r="C23">
         <f ca="1">VLOOKUP(F23,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>92</v>
+        <v>1362</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="0"/>
-        <v>0.56000000000000005</v>
+        <v>71.17</v>
       </c>
       <c r="E23" s="2">
         <v>45936</v>
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(53, 92, 0.56, '2025-10-06'),</v>
+        <v>(53, 1362, 71.17, '2025-10-06'),</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1223,22 +1223,22 @@
       </c>
       <c r="C24">
         <f ca="1">VLOOKUP(F24,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1992</v>
+        <v>723</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5</v>
+        <v>61.01</v>
       </c>
       <c r="E24" s="2">
         <v>45965</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(98, 1992, 0.5, '2025-11-04'),</v>
+        <v>(98, 723, 61.01, '2025-11-04'),</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="0"/>
-        <v>0.37</v>
+        <v>62.51</v>
       </c>
       <c r="E25" s="2">
         <v>45985</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G25" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(44, 1520, 0.37, '2025-11-24'),</v>
+        <v>(44, 1520, 62.51, '2025-11-24'),</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C26">
         <f ca="1">VLOOKUP(F26,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>50</v>
+        <v>1362</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="0"/>
-        <v>0.98</v>
+        <v>53.43</v>
       </c>
       <c r="E26" s="2">
         <v>45994</v>
       </c>
       <c r="F26">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(95, 50, 0.98, '2025-12-03'),</v>
+        <v>(95, 1362, 53.43, '2025-12-03'),</v>
       </c>
     </row>
   </sheetData>
